--- a/salidas/empresas/DE.xlsx
+++ b/salidas/empresas/DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>24.29889678955078</v>
+        <v>24.29890060424805</v>
       </c>
       <c r="C2" t="n">
         <v>35.88000106811523</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.82604217529297</v>
+        <v>25.8260440826416</v>
       </c>
       <c r="C3" t="n">
         <v>38.1349983215332</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.90034866333008</v>
+        <v>26.90035820007324</v>
       </c>
       <c r="C4" t="n">
         <v>39.52500152587891</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>29.87114715576172</v>
+        <v>29.87112998962402</v>
       </c>
       <c r="C5" t="n">
         <v>43.88999938964844</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>29.1292896270752</v>
+        <v>29.1292839050293</v>
       </c>
       <c r="C6" t="n">
         <v>42.79999923706055</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>24.81640815734863</v>
+        <v>24.81640243530273</v>
       </c>
       <c r="C8" t="n">
         <v>36.28499984741211</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>26.70747756958008</v>
+        <v>26.70747375488281</v>
       </c>
       <c r="C9" t="n">
         <v>39.04999923706055</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.83004760742188</v>
+        <v>28.83005905151367</v>
       </c>
       <c r="C10" t="n">
         <v>41.95500183105469</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>29.24920845031738</v>
+        <v>29.24921798706055</v>
       </c>
       <c r="C11" t="n">
         <v>42.56499862670898</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>32.98396301269531</v>
+        <v>32.98395919799805</v>
       </c>
       <c r="C12" t="n">
         <v>48</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>32.81531143188477</v>
+        <v>32.8153190612793</v>
       </c>
       <c r="C13" t="n">
         <v>47.53499984741211</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>37.37846755981445</v>
+        <v>37.37847137451172</v>
       </c>
       <c r="C15" t="n">
         <v>54.14500045776367</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>37.65177917480469</v>
+        <v>37.65177536010742</v>
       </c>
       <c r="C16" t="n">
         <v>54.31999969482422</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>41.75174331665039</v>
+        <v>41.75175094604492</v>
       </c>
       <c r="C18" t="n">
         <v>60.23500061035156</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>41.99858856201172</v>
+        <v>41.99859237670898</v>
       </c>
       <c r="C19" t="n">
         <v>60.36999893188477</v>
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>47.32754135131836</v>
+        <v>47.32754898071289</v>
       </c>
       <c r="C21" t="n">
         <v>68.02999877929688</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>54.07106781005859</v>
+        <v>54.07107543945312</v>
       </c>
       <c r="C23" t="n">
         <v>77.44999694824219</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>59.97035980224609</v>
+        <v>59.97037506103516</v>
       </c>
       <c r="C24" t="n">
         <v>85.90000152587891</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>65.18679046630859</v>
+        <v>65.18680572509766</v>
       </c>
       <c r="C25" t="n">
         <v>93.12000274658203</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>59.64955139160156</v>
+        <v>59.64957809448242</v>
       </c>
       <c r="C27" t="n">
         <v>85.20999908447266</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>56.48516845703125</v>
+        <v>56.48517990112305</v>
       </c>
       <c r="C28" t="n">
         <v>80.44000244140625</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>59.03414535522461</v>
+        <v>59.03416061401367</v>
       </c>
       <c r="C29" t="n">
         <v>84.06999969482422</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>57.11713790893555</v>
+        <v>57.11713409423828</v>
       </c>
       <c r="C30" t="n">
         <v>81.33999633789062</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>49.45475006103516</v>
+        <v>49.45476531982422</v>
       </c>
       <c r="C32" t="n">
         <v>70.16000366210938</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>49.74374771118164</v>
+        <v>49.7437629699707</v>
       </c>
       <c r="C33" t="n">
         <v>70.56999969482422</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>35.06180191040039</v>
+        <v>35.06179046630859</v>
       </c>
       <c r="C34" t="n">
         <v>49.5</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>24.65658760070801</v>
+        <v>24.65658950805664</v>
       </c>
       <c r="C36" t="n">
         <v>34.81000137329102</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>27.34179306030273</v>
+        <v>27.34178352355957</v>
       </c>
       <c r="C37" t="n">
         <v>38.31999969482422</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>24.78741836547852</v>
+        <v>24.78741645812988</v>
       </c>
       <c r="C38" t="n">
         <v>34.7400016784668</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.61445045471191</v>
+        <v>19.61445808410645</v>
       </c>
       <c r="C39" t="n">
         <v>27.48999977111816</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>23.63739967346191</v>
+        <v>23.63740158081055</v>
       </c>
       <c r="C40" t="n">
         <v>32.86999893188477</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>29.67079734802246</v>
+        <v>29.67079925537109</v>
       </c>
       <c r="C41" t="n">
         <v>41.2599983215332</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.26007080078125</v>
+        <v>31.26005554199219</v>
       </c>
       <c r="C42" t="n">
         <v>43.47000122070312</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>28.92106246948242</v>
+        <v>28.92105865478516</v>
       </c>
       <c r="C43" t="n">
         <v>39.95000076293945</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>31.66474914550781</v>
+        <v>31.66475868225098</v>
       </c>
       <c r="C44" t="n">
         <v>43.7400016784668</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>31.56339836120605</v>
+        <v>31.56341552734375</v>
       </c>
       <c r="C45" t="n">
         <v>43.59999847412109</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>31.2704029083252</v>
+        <v>31.27040672302246</v>
       </c>
       <c r="C46" t="n">
         <v>42.91999816894531</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>33.18655014038086</v>
+        <v>33.18655395507812</v>
       </c>
       <c r="C47" t="n">
         <v>45.54999923706055</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>38.98600387573242</v>
+        <v>38.98598861694336</v>
       </c>
       <c r="C48" t="n">
         <v>53.5099983215332</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>39.60686492919922</v>
+        <v>39.60685348510742</v>
       </c>
       <c r="C49" t="n">
         <v>54.09000015258789</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>36.57538604736328</v>
+        <v>36.57537078857422</v>
       </c>
       <c r="C50" t="n">
         <v>49.95000076293945</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.95734786987305</v>
+        <v>41.95735168457031</v>
       </c>
       <c r="C51" t="n">
         <v>57.29999923706055</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>43.74121475219727</v>
+        <v>43.74123001098633</v>
       </c>
       <c r="C52" t="n">
         <v>59.45999908447266</v>
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>42.43178558349609</v>
+        <v>42.43178939819336</v>
       </c>
       <c r="C54" t="n">
         <v>57.68000030517578</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>41.167236328125</v>
+        <v>41.16723251342773</v>
       </c>
       <c r="C55" t="n">
         <v>55.68000030517578</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>49.30013275146484</v>
+        <v>49.30011749267578</v>
       </c>
       <c r="C56" t="n">
         <v>66.68000030517578</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>46.77892303466797</v>
+        <v>46.77893829345703</v>
       </c>
       <c r="C57" t="n">
         <v>63.27000045776367</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>51.80767440795898</v>
+        <v>51.80768203735352</v>
       </c>
       <c r="C58" t="n">
         <v>69.77999877929688</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>57.01963043212891</v>
+        <v>57.0196418762207</v>
       </c>
       <c r="C59" t="n">
         <v>76.80000305175781</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>55.46051406860352</v>
+        <v>55.46051788330078</v>
       </c>
       <c r="C60" t="n">
         <v>74.69999694824219</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>61.91935348510742</v>
+        <v>61.91936111450195</v>
       </c>
       <c r="C61" t="n">
         <v>83.05000305175781</v>
@@ -1728,11 +1740,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>67.77201843261719</v>
+        <v>67.77204895019531</v>
       </c>
       <c r="C62" t="n">
         <v>90.90000152587891</v>
@@ -1757,11 +1769,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>67.21287536621094</v>
+        <v>67.21286773681641</v>
       </c>
       <c r="C63" t="n">
         <v>90.15000152587891</v>
@@ -1786,11 +1798,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>72.51000213623047</v>
+        <v>72.51002502441406</v>
       </c>
       <c r="C64" t="n">
         <v>96.88999938964844</v>
@@ -1815,11 +1827,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>72.96652984619141</v>
+        <v>72.96651458740234</v>
       </c>
       <c r="C65" t="n">
         <v>97.5</v>
@@ -1844,7 +1856,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1873,11 +1885,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>62.01859664916992</v>
+        <v>62.01858520507812</v>
       </c>
       <c r="C67" t="n">
         <v>82.44999694824219</v>
@@ -1902,11 +1914,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>59.05496215820312</v>
+        <v>59.0549201965332</v>
       </c>
       <c r="C68" t="n">
         <v>78.51000213623047</v>
@@ -1931,11 +1943,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>60.79252624511719</v>
+        <v>60.79250335693359</v>
       </c>
       <c r="C69" t="n">
         <v>80.81999969482422</v>
@@ -1960,11 +1972,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>48.85761642456055</v>
+        <v>48.85762405395508</v>
       </c>
       <c r="C70" t="n">
         <v>64.56999969482422</v>
@@ -1989,11 +2001,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>57.43061447143555</v>
+        <v>57.43059539794922</v>
       </c>
       <c r="C71" t="n">
         <v>75.90000152587891</v>
@@ -2018,11 +2030,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>59.96543502807617</v>
+        <v>59.96543884277344</v>
       </c>
       <c r="C72" t="n">
         <v>79.25</v>
@@ -2047,11 +2059,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>58.83529281616211</v>
+        <v>58.83528900146484</v>
       </c>
       <c r="C73" t="n">
         <v>77.34999847412109</v>
@@ -2076,11 +2088,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>65.52889251708984</v>
+        <v>65.52890014648438</v>
       </c>
       <c r="C74" t="n">
         <v>86.15000152587891</v>
@@ -2105,11 +2117,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>63.07966995239258</v>
+        <v>63.07962417602539</v>
       </c>
       <c r="C75" t="n">
         <v>82.93000030517578</v>
@@ -2134,11 +2146,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>61.88100814819336</v>
+        <v>61.88100051879883</v>
       </c>
       <c r="C76" t="n">
         <v>80.90000152587891</v>
@@ -2163,11 +2175,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>62.99776840209961</v>
+        <v>62.99775695800781</v>
       </c>
       <c r="C77" t="n">
         <v>82.36000061035156</v>
@@ -2192,11 +2204,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>56.50369644165039</v>
+        <v>56.50370025634766</v>
       </c>
       <c r="C78" t="n">
         <v>73.87000274658203</v>
@@ -2221,7 +2233,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2250,11 +2262,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>59.11799621582031</v>
+        <v>59.11798095703125</v>
       </c>
       <c r="C80" t="n">
         <v>76.81999969482422</v>
@@ -2279,11 +2291,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>57.80201721191406</v>
+        <v>57.80204010009766</v>
       </c>
       <c r="C81" t="n">
         <v>75.11000061035156</v>
@@ -2308,11 +2320,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>63.82564926147461</v>
+        <v>63.82561492919922</v>
       </c>
       <c r="C82" t="n">
         <v>82.47000122070312</v>
@@ -2337,7 +2349,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2366,11 +2378,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>65.04842376708984</v>
+        <v>65.04843902587891</v>
       </c>
       <c r="C84" t="n">
         <v>84.05000305175781</v>
@@ -2395,11 +2407,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>67.24013519287109</v>
+        <v>67.24012756347656</v>
       </c>
       <c r="C85" t="n">
         <v>86.41999816894531</v>
@@ -2424,11 +2436,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>73.18451690673828</v>
+        <v>73.18450927734375</v>
       </c>
       <c r="C86" t="n">
         <v>94.05999755859375</v>
@@ -2453,11 +2465,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>68.33718109130859</v>
+        <v>68.33719635009766</v>
       </c>
       <c r="C87" t="n">
         <v>87.83000183105469</v>
@@ -2482,11 +2494,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>67.29279327392578</v>
+        <v>67.29280090332031</v>
       </c>
       <c r="C88" t="n">
         <v>85.98000335693359</v>
@@ -2511,11 +2523,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>69.89125061035156</v>
+        <v>69.8912353515625</v>
       </c>
       <c r="C89" t="n">
         <v>89.30000305175781</v>
@@ -2540,11 +2552,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>68.17720794677734</v>
+        <v>68.17718505859375</v>
       </c>
       <c r="C90" t="n">
         <v>87.11000061035156</v>
@@ -2569,11 +2581,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>63.98664474487305</v>
+        <v>63.98660278320312</v>
       </c>
       <c r="C91" t="n">
         <v>81.25</v>
@@ -2598,11 +2610,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>65.41993713378906</v>
+        <v>65.41994476318359</v>
       </c>
       <c r="C92" t="n">
         <v>83.06999969482422</v>
@@ -2627,11 +2639,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>65.86881256103516</v>
+        <v>65.86882781982422</v>
       </c>
       <c r="C93" t="n">
         <v>83.63999938964844</v>
@@ -2656,11 +2668,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>64.48545837402344</v>
+        <v>64.48544311523438</v>
       </c>
       <c r="C94" t="n">
         <v>81.38999938964844</v>
@@ -2685,11 +2697,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>64.84196472167969</v>
+        <v>64.84197998046875</v>
       </c>
       <c r="C95" t="n">
         <v>81.83999633789062</v>
@@ -2714,11 +2726,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>66.74349212646484</v>
+        <v>66.74348449707031</v>
       </c>
       <c r="C96" t="n">
         <v>84.23999786376953</v>
@@ -2743,11 +2755,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>72.7681884765625</v>
+        <v>72.76822662353516</v>
       </c>
       <c r="C97" t="n">
         <v>91.33000183105469</v>
@@ -2772,11 +2784,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>68.48957061767578</v>
+        <v>68.48958587646484</v>
       </c>
       <c r="C98" t="n">
         <v>85.95999908447266</v>
@@ -2801,11 +2813,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>68.4656982421875</v>
+        <v>68.46567535400391</v>
       </c>
       <c r="C99" t="n">
         <v>85.93000030517578</v>
@@ -2830,11 +2842,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>72.76607513427734</v>
+        <v>72.76605224609375</v>
       </c>
       <c r="C100" t="n">
         <v>90.80000305175781</v>
@@ -2859,7 +2871,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2888,11 +2900,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>73.06256866455078</v>
+        <v>73.06254577636719</v>
       </c>
       <c r="C102" t="n">
         <v>91.16999816894531</v>
@@ -2917,11 +2929,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>73.04871368408203</v>
+        <v>73.04872131347656</v>
       </c>
       <c r="C103" t="n">
         <v>90.55000305175781</v>
@@ -2946,11 +2958,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>68.66016387939453</v>
+        <v>68.66014862060547</v>
       </c>
       <c r="C104" t="n">
         <v>85.11000061035156</v>
@@ -2975,11 +2987,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>67.83728790283203</v>
+        <v>67.83731079101562</v>
       </c>
       <c r="C105" t="n">
         <v>84.08999633789062</v>
@@ -3004,11 +3016,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>66.62403869628906</v>
+        <v>66.62404632568359</v>
       </c>
       <c r="C106" t="n">
         <v>81.98999786376953</v>
@@ -3033,7 +3045,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3062,11 +3074,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>70.38629913330078</v>
+        <v>70.38633728027344</v>
       </c>
       <c r="C108" t="n">
         <v>86.62000274658203</v>
@@ -3091,7 +3103,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3120,11 +3132,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>69.68768310546875</v>
+        <v>69.68769073486328</v>
       </c>
       <c r="C110" t="n">
         <v>85.19000244140625</v>
@@ -3149,11 +3161,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>74.11322784423828</v>
+        <v>74.11319732666016</v>
       </c>
       <c r="C111" t="n">
         <v>90.59999847412109</v>
@@ -3178,11 +3190,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>72.22514343261719</v>
+        <v>72.22512054443359</v>
       </c>
       <c r="C112" t="n">
         <v>87.69000244140625</v>
@@ -3207,11 +3219,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>74.55603790283203</v>
+        <v>74.55602264404297</v>
       </c>
       <c r="C113" t="n">
         <v>90.51999664306641</v>
@@ -3236,7 +3248,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3265,11 +3277,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>80.44792175292969</v>
+        <v>80.44789886474609</v>
       </c>
       <c r="C115" t="n">
         <v>97.05000305175781</v>
@@ -3294,11 +3306,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>78.39216613769531</v>
+        <v>78.39215087890625</v>
       </c>
       <c r="C116" t="n">
         <v>94.56999969482422</v>
@@ -3323,11 +3335,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>67.79010772705078</v>
+        <v>67.79011535644531</v>
       </c>
       <c r="C117" t="n">
         <v>81.77999877929688</v>
@@ -3352,11 +3364,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>61.83037948608398</v>
+        <v>61.83039093017578</v>
       </c>
       <c r="C118" t="n">
         <v>74</v>
@@ -3381,11 +3393,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>65.17255401611328</v>
+        <v>65.17253112792969</v>
       </c>
       <c r="C119" t="n">
         <v>78</v>
@@ -3410,11 +3422,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>66.48435211181641</v>
+        <v>66.48433685302734</v>
       </c>
       <c r="C120" t="n">
         <v>79.56999969482422</v>
@@ -3439,7 +3451,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3468,11 +3480,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>64.84436798095703</v>
+        <v>64.84437561035156</v>
       </c>
       <c r="C122" t="n">
         <v>77.01000213623047</v>
@@ -3497,11 +3509,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>67.51358795166016</v>
+        <v>67.51356506347656</v>
       </c>
       <c r="C123" t="n">
         <v>80.18000030517578</v>
@@ -3526,11 +3538,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>65.31635284423828</v>
+        <v>65.31634521484375</v>
       </c>
       <c r="C124" t="n">
         <v>76.98999786376953</v>
@@ -3555,11 +3567,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>71.35678863525391</v>
+        <v>71.35679626464844</v>
       </c>
       <c r="C125" t="n">
         <v>84.11000061035156</v>
@@ -3584,11 +3596,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>69.812744140625</v>
+        <v>69.81276702880859</v>
       </c>
       <c r="C126" t="n">
         <v>82.29000091552734</v>
@@ -3613,11 +3625,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>69.26802825927734</v>
+        <v>69.26806640625</v>
       </c>
       <c r="C127" t="n">
         <v>81.04000091552734</v>
@@ -3642,11 +3654,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>66.42178344726562</v>
+        <v>66.4217529296875</v>
       </c>
       <c r="C128" t="n">
         <v>77.70999908447266</v>
@@ -3671,11 +3683,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>72.26817321777344</v>
+        <v>72.2681884765625</v>
       </c>
       <c r="C129" t="n">
         <v>84.55000305175781</v>
@@ -3700,11 +3712,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>73.48284912109375</v>
+        <v>73.48284149169922</v>
       </c>
       <c r="C130" t="n">
         <v>85.34999847412109</v>
@@ -3729,11 +3741,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>76.02266693115234</v>
+        <v>76.02268218994141</v>
       </c>
       <c r="C131" t="n">
         <v>88.30000305175781</v>
@@ -3758,11 +3770,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>86.26807403564453</v>
+        <v>86.26808166503906</v>
       </c>
       <c r="C132" t="n">
         <v>100.1999969482422</v>
@@ -3787,11 +3799,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>89.22847747802734</v>
+        <v>89.22848510742188</v>
       </c>
       <c r="C133" t="n">
         <v>103.0400009155273</v>
@@ -3816,7 +3828,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3845,11 +3857,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>94.81391906738281</v>
+        <v>94.81393432617188</v>
       </c>
       <c r="C135" t="n">
         <v>109.4899978637695</v>
@@ -3874,11 +3886,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>94.79341888427734</v>
+        <v>94.79339599609375</v>
       </c>
       <c r="C136" t="n">
         <v>108.8600006103516</v>
@@ -3903,11 +3915,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>97.18804168701172</v>
+        <v>97.18804931640625</v>
       </c>
       <c r="C137" t="n">
         <v>111.6100006103516</v>
@@ -3932,11 +3944,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>106.6360549926758</v>
+        <v>106.6360626220703</v>
       </c>
       <c r="C138" t="n">
         <v>122.4599990844727</v>
@@ -3961,11 +3973,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>108.1519317626953</v>
+        <v>108.1519165039062</v>
       </c>
       <c r="C139" t="n">
         <v>123.5899963378906</v>
@@ -3990,11 +4002,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>112.2560577392578</v>
+        <v>112.2560653686523</v>
       </c>
       <c r="C140" t="n">
         <v>128.2799987792969</v>
@@ -4019,11 +4031,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>101.4487762451172</v>
+        <v>101.4487533569336</v>
       </c>
       <c r="C141" t="n">
         <v>115.9300003051758</v>
@@ -4048,7 +4060,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4077,11 +4089,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>116.8499984741211</v>
+        <v>116.8500289916992</v>
       </c>
       <c r="C143" t="n">
         <v>132.8800048828125</v>
@@ -4106,11 +4118,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>131.7816314697266</v>
+        <v>131.7816162109375</v>
       </c>
       <c r="C144" t="n">
         <v>149.8600006103516</v>
@@ -4135,11 +4147,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>138.1520690917969</v>
+        <v>138.152099609375</v>
       </c>
       <c r="C145" t="n">
         <v>156.5099945068359</v>
@@ -4164,11 +4176,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>146.8996887207031</v>
+        <v>146.8996734619141</v>
       </c>
       <c r="C146" t="n">
         <v>166.4199981689453</v>
@@ -4193,7 +4205,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4222,11 +4234,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>137.6444702148438</v>
+        <v>137.6444854736328</v>
       </c>
       <c r="C148" t="n">
         <v>155.3200073242188</v>
@@ -4251,11 +4263,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>119.9293212890625</v>
+        <v>119.929328918457</v>
       </c>
       <c r="C149" t="n">
         <v>135.3300018310547</v>
@@ -4280,11 +4292,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>132.4956207275391</v>
+        <v>132.4956512451172</v>
       </c>
       <c r="C150" t="n">
         <v>149.5099945068359</v>
@@ -4309,11 +4321,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>124.5070037841797</v>
+        <v>124.5070114135742</v>
       </c>
       <c r="C151" t="n">
         <v>139.8000030517578</v>
@@ -4338,11 +4350,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>128.9511108398438</v>
+        <v>128.9511413574219</v>
       </c>
       <c r="C152" t="n">
         <v>144.7899932861328</v>
@@ -4367,11 +4379,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>128.0694427490234</v>
+        <v>128.0694580078125</v>
       </c>
       <c r="C153" t="n">
         <v>143.8000030517578</v>
@@ -4396,11 +4408,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>134.494384765625</v>
+        <v>134.4943695068359</v>
       </c>
       <c r="C154" t="n">
         <v>150.3300018310547</v>
@@ -4425,11 +4437,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>121.1728897094727</v>
+        <v>121.1728744506836</v>
       </c>
       <c r="C155" t="n">
         <v>135.4400024414062</v>
@@ -4454,11 +4466,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>138.5650787353516</v>
+        <v>138.5650482177734</v>
       </c>
       <c r="C156" t="n">
         <v>154.8800048828125</v>
@@ -4483,11 +4495,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>134.1514892578125</v>
+        <v>134.1514434814453</v>
       </c>
       <c r="C157" t="n">
         <v>149.1699981689453</v>
@@ -4512,11 +4524,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>147.4883880615234</v>
+        <v>147.4883575439453</v>
       </c>
       <c r="C158" t="n">
         <v>164</v>
@@ -4541,7 +4553,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4570,11 +4582,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>144.4407348632812</v>
+        <v>144.4407653808594</v>
       </c>
       <c r="C160" t="n">
         <v>159.8399963378906</v>
@@ -4599,11 +4611,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>149.6729431152344</v>
+        <v>149.6729736328125</v>
       </c>
       <c r="C161" t="n">
         <v>165.6300048828125</v>
@@ -4628,11 +4640,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>126.6658096313477</v>
+        <v>126.6658477783203</v>
       </c>
       <c r="C162" t="n">
         <v>140.1699981689453</v>
@@ -4657,11 +4669,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>150.4334869384766</v>
+        <v>150.4335174560547</v>
       </c>
       <c r="C163" t="n">
         <v>165.7100067138672</v>
@@ -4686,11 +4698,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>150.3790130615234</v>
+        <v>150.3790435791016</v>
       </c>
       <c r="C164" t="n">
         <v>165.6499938964844</v>
@@ -4715,11 +4727,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>140.6291656494141</v>
+        <v>140.6291198730469</v>
       </c>
       <c r="C165" t="n">
         <v>154.9100036621094</v>
@@ -4744,11 +4756,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>153.8322448730469</v>
+        <v>153.8322601318359</v>
       </c>
       <c r="C166" t="n">
         <v>168.6799926757812</v>
@@ -4773,11 +4785,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>158.8116455078125</v>
+        <v>158.8116149902344</v>
       </c>
       <c r="C167" t="n">
         <v>174.1399993896484</v>
@@ -4802,11 +4814,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>153.2576751708984</v>
+        <v>153.2577056884766</v>
       </c>
       <c r="C168" t="n">
         <v>168.0500030517578</v>
@@ -4831,11 +4843,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>158.6951446533203</v>
+        <v>158.6950988769531</v>
       </c>
       <c r="C169" t="n">
         <v>173.2599945068359</v>
@@ -4860,11 +4872,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>145.2491455078125</v>
+        <v>145.2491302490234</v>
       </c>
       <c r="C170" t="n">
         <v>158.5800018310547</v>
@@ -4889,11 +4901,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>143.32568359375</v>
+        <v>143.3257293701172</v>
       </c>
       <c r="C171" t="n">
         <v>156.4799957275391</v>
@@ -4918,11 +4930,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>127.261604309082</v>
+        <v>127.2616348266602</v>
       </c>
       <c r="C172" t="n">
         <v>138.1600036621094</v>
@@ -4947,11 +4959,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>133.6173248291016</v>
+        <v>133.6173095703125</v>
       </c>
       <c r="C173" t="n">
         <v>145.0599975585938</v>
@@ -4976,11 +4988,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>140.1203918457031</v>
+        <v>140.1204223632812</v>
       </c>
       <c r="C174" t="n">
         <v>152.1199951171875</v>
@@ -5005,11 +5017,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>145.4955139160156</v>
+        <v>145.4955749511719</v>
       </c>
       <c r="C175" t="n">
         <v>157.1499938964844</v>
@@ -5034,11 +5046,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>163.2345886230469</v>
+        <v>163.2346343994141</v>
       </c>
       <c r="C176" t="n">
         <v>176.3099975585938</v>
@@ -5063,11 +5075,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>194.481689453125</v>
+        <v>194.4816589355469</v>
       </c>
       <c r="C177" t="n">
         <v>210.0599975585938</v>
@@ -5092,11 +5104,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>205.8988647460938</v>
+        <v>205.8988189697266</v>
       </c>
       <c r="C178" t="n">
         <v>221.6300048828125</v>
@@ -5121,11 +5133,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>209.8750305175781</v>
+        <v>209.8750152587891</v>
       </c>
       <c r="C179" t="n">
         <v>225.9100036621094</v>
@@ -5150,11 +5162,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>243.0503997802734</v>
+        <v>243.0503387451172</v>
       </c>
       <c r="C180" t="n">
         <v>261.6199951171875</v>
@@ -5179,11 +5191,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>250.6709289550781</v>
+        <v>250.6710205078125</v>
       </c>
       <c r="C181" t="n">
         <v>269.0499877929688</v>
@@ -5208,11 +5220,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>269.0718688964844</v>
+        <v>269.07177734375</v>
       </c>
       <c r="C182" t="n">
         <v>288.7999877929688</v>
@@ -5237,11 +5249,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>325.2713012695312</v>
+        <v>325.2712707519531</v>
       </c>
       <c r="C183" t="n">
         <v>349.1199951171875</v>
@@ -5266,11 +5278,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>349.4369201660156</v>
+        <v>349.4368591308594</v>
       </c>
       <c r="C184" t="n">
         <v>374.1400146484375</v>
@@ -5295,11 +5307,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>346.3640441894531</v>
+        <v>346.3640747070312</v>
       </c>
       <c r="C185" t="n">
         <v>370.8500061035156</v>
@@ -5324,11 +5336,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>337.2577819824219</v>
+        <v>337.2578735351562</v>
       </c>
       <c r="C186" t="n">
         <v>361.1000061035156</v>
@@ -5353,11 +5365,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>330.2713623046875</v>
+        <v>330.2712707519531</v>
       </c>
       <c r="C187" t="n">
         <v>352.7099914550781</v>
@@ -5382,11 +5394,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>338.5864868164062</v>
+        <v>338.58642578125</v>
       </c>
       <c r="C188" t="n">
         <v>361.5899963378906</v>
@@ -5411,11 +5423,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>353.9805603027344</v>
+        <v>353.9804992675781</v>
       </c>
       <c r="C189" t="n">
         <v>378.0299987792969</v>
@@ -5440,11 +5452,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>314.6870727539062</v>
+        <v>314.6871032714844</v>
       </c>
       <c r="C190" t="n">
         <v>335.0700073242188</v>
@@ -5469,11 +5481,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>321.4867248535156</v>
+        <v>321.4866638183594</v>
       </c>
       <c r="C191" t="n">
         <v>342.3099975585938</v>
@@ -5498,11 +5510,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>324.5201721191406</v>
+        <v>324.5202026367188</v>
       </c>
       <c r="C192" t="n">
         <v>345.5400085449219</v>
@@ -5527,11 +5539,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>323.0124206542969</v>
+        <v>323.0124816894531</v>
       </c>
       <c r="C193" t="n">
         <v>342.8900146484375</v>
@@ -5556,11 +5568,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>354.5798950195312</v>
+        <v>354.579833984375</v>
       </c>
       <c r="C194" t="n">
         <v>376.3999938964844</v>
@@ -5585,7 +5597,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5614,11 +5626,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>392.3732604980469</v>
+        <v>392.373291015625</v>
       </c>
       <c r="C196" t="n">
         <v>415.4599914550781</v>
@@ -5643,7 +5655,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5672,11 +5684,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>337.8985290527344</v>
+        <v>337.8984985351562</v>
       </c>
       <c r="C198" t="n">
         <v>357.7799987792969</v>
@@ -5701,11 +5713,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>283.8662719726562</v>
+        <v>283.8663024902344</v>
       </c>
       <c r="C199" t="n">
         <v>299.4700012207031</v>
@@ -5730,11 +5742,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>325.2988586425781</v>
+        <v>325.298828125</v>
       </c>
       <c r="C200" t="n">
         <v>343.1799926757812</v>
@@ -5759,7 +5771,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5788,11 +5800,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>317.5301513671875</v>
+        <v>317.5301818847656</v>
       </c>
       <c r="C202" t="n">
         <v>333.8900146484375</v>
@@ -5817,11 +5829,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>376.4257202148438</v>
+        <v>376.4257507324219</v>
       </c>
       <c r="C203" t="n">
         <v>395.8200073242188</v>
@@ -5846,11 +5858,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>419.3919982910156</v>
+        <v>419.3920593261719</v>
       </c>
       <c r="C204" t="n">
         <v>441</v>
@@ -5875,11 +5887,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>408.8924560546875</v>
+        <v>408.8923950195312</v>
       </c>
       <c r="C205" t="n">
         <v>428.760009765625</v>
@@ -5904,11 +5916,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>403.2466735839844</v>
+        <v>403.2467346191406</v>
       </c>
       <c r="C206" t="n">
         <v>422.8399963378906</v>
@@ -5933,11 +5945,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>399.8134765625</v>
+        <v>399.8135070800781</v>
       </c>
       <c r="C207" t="n">
         <v>419.239990234375</v>
@@ -5962,11 +5974,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>394.9801025390625</v>
+        <v>394.9801330566406</v>
       </c>
       <c r="C208" t="n">
         <v>412.8800048828125</v>
@@ -5991,11 +6003,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>361.6313781738281</v>
+        <v>361.6314392089844</v>
       </c>
       <c r="C209" t="n">
         <v>378.0199890136719</v>
@@ -6020,11 +6032,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>330.9804992675781</v>
+        <v>330.9804382324219</v>
       </c>
       <c r="C210" t="n">
         <v>345.9800109863281</v>
@@ -6049,11 +6061,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>388.8229370117188</v>
+        <v>388.8229675292969</v>
       </c>
       <c r="C211" t="n">
         <v>405.1900024414062</v>
@@ -6078,11 +6090,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>412.2470092773438</v>
+        <v>412.2469787597656</v>
       </c>
       <c r="C212" t="n">
         <v>429.6000061035156</v>
@@ -6107,7 +6119,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6136,11 +6148,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>363.4127502441406</v>
+        <v>363.4127197265625</v>
       </c>
       <c r="C214" t="n">
         <v>377.3800048828125</v>
@@ -6165,11 +6177,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>351.8375854492188</v>
+        <v>351.8375549316406</v>
       </c>
       <c r="C215" t="n">
         <v>365.3599853515625</v>
@@ -6194,11 +6206,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>350.9227600097656</v>
+        <v>350.9228210449219</v>
       </c>
       <c r="C216" t="n">
         <v>364.4100036621094</v>
@@ -6223,11 +6235,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>386.4848937988281</v>
+        <v>386.48486328125</v>
       </c>
       <c r="C217" t="n">
         <v>399.8699951171875</v>
@@ -6252,7 +6264,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6281,7 +6293,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6310,11 +6322,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>398.4607849121094</v>
+        <v>398.4608154296875</v>
       </c>
       <c r="C220" t="n">
         <v>410.739990234375</v>
@@ -6339,11 +6351,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>379.7087097167969</v>
+        <v>379.7086486816406</v>
       </c>
       <c r="C221" t="n">
         <v>391.4100036621094</v>
@@ -6368,7 +6380,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6397,11 +6409,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>363.8798828125</v>
+        <v>363.8798217773438</v>
       </c>
       <c r="C223" t="n">
         <v>373.6300048828125</v>
@@ -6426,7 +6438,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6455,11 +6467,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>375.6737670898438</v>
+        <v>375.6738586425781</v>
       </c>
       <c r="C225" t="n">
         <v>385.739990234375</v>
@@ -6484,11 +6496,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>407.8739013671875</v>
+        <v>407.8738708496094</v>
       </c>
       <c r="C226" t="n">
         <v>417.3299865722656</v>
@@ -6513,7 +6525,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6542,11 +6554,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>455.3432922363281</v>
+        <v>455.3433227539062</v>
       </c>
       <c r="C228" t="n">
         <v>465.8999938964844</v>
@@ -6571,11 +6583,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>415.6853942871094</v>
+        <v>415.6853637695312</v>
       </c>
       <c r="C229" t="n">
         <v>423.7000122070312</v>
@@ -6600,11 +6612,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>467.5455017089844</v>
+        <v>467.5454711914062</v>
       </c>
       <c r="C230" t="n">
         <v>476.5599975585938</v>
@@ -6629,7 +6641,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6658,11 +6670,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>462.0806274414062</v>
+        <v>462.0805969238281</v>
       </c>
       <c r="C232" t="n">
         <v>469.3500061035156</v>
@@ -6687,7 +6699,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6716,7 +6728,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6745,7 +6757,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6774,7 +6786,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6803,7 +6815,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6832,7 +6844,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6861,7 +6873,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6890,7 +6902,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6919,7 +6931,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6948,7 +6960,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6977,7 +6989,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7006,7 +7018,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7035,7 +7047,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7064,7 +7076,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7093,7 +7105,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7122,7 +7134,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7151,7 +7163,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7180,32 +7192,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>709.47998046875</v>
+        <v>694.9400024414062</v>
       </c>
       <c r="C250" t="n">
-        <v>709.47998046875</v>
+        <v>694.9400024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>22725000</v>
+        <v>23900500</v>
       </c>
       <c r="E250" t="n">
         <v>17.99</v>
       </c>
       <c r="F250" t="n">
-        <v>39.43746417280434</v>
+        <v>38.62923860152342</v>
       </c>
       <c r="G250" t="n">
         <v>269625412</v>
       </c>
       <c r="H250" t="n">
-        <v>191293832039.6387</v>
+        <v>187373484473.5452</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08428359860976309</v>
+        <v>0.08864335087228351</v>
       </c>
     </row>
   </sheetData>
@@ -7237,75 +7249,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39569</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39660</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7341,13 +7353,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39753</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39844</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7383,13 +7395,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39933</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7425,13 +7437,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7467,13 +7479,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7500,7 +7512,7 @@
       <c r="I6" t="n">
         <v>2.05</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K6" t="n">
@@ -7513,13 +7525,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7546,7 +7558,7 @@
       <c r="I7" t="n">
         <v>2.14</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K7" t="n">
@@ -7559,13 +7571,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7592,7 +7604,7 @@
       <c r="I8" t="n">
         <v>2.31</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K8" t="n">
@@ -7605,13 +7617,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7638,7 +7650,7 @@
       <c r="I9" t="n">
         <v>2.76</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K9" t="n">
@@ -7651,13 +7663,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7684,7 +7696,7 @@
       <c r="I10" t="n">
         <v>4.36</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K10" t="n">
@@ -7697,13 +7709,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7730,7 +7742,7 @@
       <c r="I11" t="n">
         <v>4.99</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7743,13 +7755,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7776,7 +7788,7 @@
       <c r="I12" t="n">
         <v>5.83</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="K12" t="n">
@@ -7789,13 +7801,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7822,7 +7834,7 @@
       <c r="I13" t="n">
         <v>6.08</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="K13" t="n">
@@ -7835,13 +7847,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40896</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7868,7 +7880,7 @@
       <c r="I14" t="n">
         <v>6.630000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40896</v>
       </c>
       <c r="K14" t="n">
@@ -7881,13 +7893,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7914,7 +7926,7 @@
       <c r="I15" t="n">
         <v>6.73</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="K15" t="n">
@@ -7927,13 +7939,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7960,7 +7972,7 @@
       <c r="I16" t="n">
         <v>7.22</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="K16" t="n">
@@ -7973,13 +7985,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41151</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8006,7 +8018,7 @@
       <c r="I17" t="n">
         <v>7.51</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41151</v>
       </c>
       <c r="K17" t="n">
@@ -8019,13 +8031,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41260</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8052,7 +8064,7 @@
       <c r="I18" t="n">
         <v>7.640000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41260</v>
       </c>
       <c r="K18" t="n">
@@ -8065,13 +8077,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8098,7 +8110,7 @@
       <c r="I19" t="n">
         <v>7.989999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8111,13 +8123,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8144,7 +8156,7 @@
       <c r="I20" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="K20" t="n">
@@ -8157,13 +8169,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41515</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8190,7 +8202,7 @@
       <c r="I21" t="n">
         <v>8.719999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41515</v>
       </c>
       <c r="K21" t="n">
@@ -8203,13 +8215,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41624</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8236,7 +8248,7 @@
       <c r="I22" t="n">
         <v>9.079999999999998</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41624</v>
       </c>
       <c r="K22" t="n">
@@ -8249,13 +8261,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8282,7 +8294,7 @@
       <c r="I23" t="n">
         <v>9.24</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8295,13 +8307,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41788</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8328,7 +8340,7 @@
       <c r="I24" t="n">
         <v>9.129999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41788</v>
       </c>
       <c r="K24" t="n">
@@ -8341,13 +8353,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41879</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8374,7 +8386,7 @@
       <c r="I25" t="n">
         <v>8.899999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41879</v>
       </c>
       <c r="K25" t="n">
@@ -8387,13 +8399,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41992</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8420,7 +8432,7 @@
       <c r="I26" t="n">
         <v>8.620000000000001</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41992</v>
       </c>
       <c r="K26" t="n">
@@ -8433,13 +8445,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8466,7 +8478,7 @@
       <c r="I27" t="n">
         <v>7.93</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K27" t="n">
@@ -8479,13 +8491,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8512,7 +8524,7 @@
       <c r="I28" t="n">
         <v>7.31</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="K28" t="n">
@@ -8525,13 +8537,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42243</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8558,7 +8570,7 @@
       <c r="I29" t="n">
         <v>6.51</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42243</v>
       </c>
       <c r="K29" t="n">
@@ -8571,13 +8583,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8604,7 +8616,7 @@
       <c r="I30" t="n">
         <v>5.76</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="K30" t="n">
@@ -8617,13 +8629,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8650,7 +8662,7 @@
       <c r="I31" t="n">
         <v>5.44</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8663,13 +8675,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42516</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8696,7 +8708,7 @@
       <c r="I32" t="n">
         <v>4.970000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42516</v>
       </c>
       <c r="K32" t="n">
@@ -8709,13 +8721,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8742,7 +8754,7 @@
       <c r="I33" t="n">
         <v>4.99</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="K33" t="n">
@@ -8755,13 +8767,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42723</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8788,7 +8800,7 @@
       <c r="I34" t="n">
         <v>4.81</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42723</v>
       </c>
       <c r="K34" t="n">
@@ -8801,13 +8813,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8834,7 +8846,7 @@
       <c r="I35" t="n">
         <v>4.62</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K35" t="n">
@@ -8847,13 +8859,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42765</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8880,7 +8892,7 @@
       <c r="I36" t="n">
         <v>5.550000000000001</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="K36" t="n">
@@ -8893,13 +8905,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8926,7 +8938,7 @@
       <c r="I37" t="n">
         <v>5.970000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="K37" t="n">
@@ -8939,13 +8951,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43087</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8972,7 +8984,7 @@
       <c r="I38" t="n">
         <v>6.640000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43087</v>
       </c>
       <c r="K38" t="n">
@@ -8985,13 +8997,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9018,7 +9030,7 @@
       <c r="I39" t="n">
         <v>4.370000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="K39" t="n">
@@ -9031,13 +9043,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43129</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43219</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9064,7 +9076,7 @@
       <c r="I40" t="n">
         <v>5.550000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="K40" t="n">
@@ -9077,13 +9089,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43310</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43342</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9110,7 +9122,7 @@
       <c r="I41" t="n">
         <v>6.36</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43342</v>
       </c>
       <c r="K41" t="n">
@@ -9123,13 +9135,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43401</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43451</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9156,7 +9168,7 @@
       <c r="I42" t="n">
         <v>7.21</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43451</v>
       </c>
       <c r="K42" t="n">
@@ -9169,13 +9181,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43492</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9202,7 +9214,7 @@
       <c r="I43" t="n">
         <v>10.41</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K43" t="n">
@@ -9215,13 +9227,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43493</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43583</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9248,7 +9260,7 @@
       <c r="I44" t="n">
         <v>10.26</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="K44" t="n">
@@ -9261,13 +9273,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43674</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43706</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9294,7 +9306,7 @@
       <c r="I45" t="n">
         <v>10.29</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43706</v>
       </c>
       <c r="K45" t="n">
@@ -9307,13 +9319,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43772</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43818</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9340,7 +9352,7 @@
       <c r="I46" t="n">
         <v>10.14</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43818</v>
       </c>
       <c r="K46" t="n">
@@ -9353,13 +9365,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43773</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43863</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9386,7 +9398,7 @@
       <c r="I47" t="n">
         <v>10.23</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K47" t="n">
@@ -9399,13 +9411,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43864</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43954</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43979</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9432,7 +9444,7 @@
       <c r="I48" t="n">
         <v>8.82</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43979</v>
       </c>
       <c r="K48" t="n">
@@ -9445,13 +9457,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43955</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44070</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9478,7 +9490,7 @@
       <c r="I49" t="n">
         <v>8.58</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44070</v>
       </c>
       <c r="K49" t="n">
@@ -9491,13 +9503,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9524,7 +9536,7 @@
       <c r="I50" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="K50" t="n">
@@ -9537,13 +9549,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44137</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9570,7 +9582,7 @@
       <c r="I51" t="n">
         <v>10.94</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K51" t="n">
@@ -9583,13 +9595,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9616,7 +9628,7 @@
       <c r="I52" t="n">
         <v>14.51</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="K52" t="n">
@@ -9629,13 +9641,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9662,7 +9674,7 @@
       <c r="I53" t="n">
         <v>17.26</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="K53" t="n">
@@ -9675,13 +9687,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9708,7 +9720,7 @@
       <c r="I54" t="n">
         <v>18.99</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="K54" t="n">
@@ -9721,13 +9733,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9754,7 +9766,7 @@
       <c r="I55" t="n">
         <v>18.04</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K55" t="n">
@@ -9767,13 +9779,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9800,7 +9812,7 @@
       <c r="I56" t="n">
         <v>19.17</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="K56" t="n">
@@ -9813,13 +9825,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9846,7 +9858,7 @@
       <c r="I57" t="n">
         <v>20.01</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="K57" t="n">
@@ -9859,13 +9871,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44910</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9892,7 +9904,7 @@
       <c r="I58" t="n">
         <v>23.28</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44910</v>
       </c>
       <c r="K58" t="n">
@@ -9905,13 +9917,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9938,7 +9950,7 @@
       <c r="I59" t="n">
         <v>26.91</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9951,13 +9963,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44956</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9984,7 +9996,7 @@
       <c r="I60" t="n">
         <v>29.75</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="K60" t="n">
@@ -9997,13 +10009,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10030,7 +10042,7 @@
       <c r="I61" t="n">
         <v>33.79</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="K61" t="n">
@@ -10043,13 +10055,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10076,7 +10088,7 @@
       <c r="I62" t="n">
         <v>34.63</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="K62" t="n">
@@ -10089,13 +10101,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10122,7 +10134,7 @@
       <c r="I63" t="n">
         <v>34.31</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="K63" t="n">
@@ -10135,13 +10147,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45320</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45410</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10168,7 +10180,7 @@
       <c r="I64" t="n">
         <v>33.19</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="K64" t="n">
@@ -10181,13 +10193,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45501</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10214,7 +10226,7 @@
       <c r="I65" t="n">
         <v>29.28</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="K65" t="n">
@@ -10227,13 +10239,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45592</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45638</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10260,7 +10272,7 @@
       <c r="I66" t="n">
         <v>25.62</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45638</v>
       </c>
       <c r="K66" t="n">
@@ -10273,13 +10285,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10306,7 +10318,7 @@
       <c r="I67" t="n">
         <v>22.58</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K67" t="n">
@@ -10319,13 +10331,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45774</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10352,7 +10364,7 @@
       <c r="I68" t="n">
         <v>20.69</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="K68" t="n">
@@ -10365,13 +10377,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45865</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10398,7 +10410,7 @@
       <c r="I69" t="n">
         <v>19.15</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="K69" t="n">
@@ -10411,13 +10423,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45866</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10444,7 +10456,7 @@
       <c r="I70" t="n">
         <v>18.5</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="K70" t="n">
@@ -10457,13 +10469,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45964</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10490,7 +10502,7 @@
       <c r="I71" t="n">
         <v>17.73</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="K71" t="n">
@@ -10503,13 +10515,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46055</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10536,7 +10548,7 @@
       <c r="I72" t="n">
         <v>17.64</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="K72" t="n">
@@ -10549,13 +10561,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46146</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46236</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10582,7 +10594,7 @@
       <c r="I73" t="n">
         <v>17.99</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K73" t="n">
@@ -10619,52 +10631,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="C2" t="n">
@@ -10693,10 +10705,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40164</v>
       </c>
       <c r="C3" t="n">
@@ -10725,10 +10737,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C4" t="n">
@@ -10757,10 +10769,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="C5" t="n">
@@ -10789,10 +10801,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="C6" t="n">
@@ -10821,10 +10833,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="C7" t="n">
@@ -10853,10 +10865,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10885,10 +10897,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40690</v>
       </c>
       <c r="C9" t="n">
@@ -10917,10 +10929,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="C10" t="n">
@@ -10949,10 +10961,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40896</v>
       </c>
       <c r="C11" t="n">
@@ -10981,10 +10993,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="C12" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="C13" t="n">
@@ -11045,10 +11057,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41151</v>
       </c>
       <c r="C14" t="n">
@@ -11077,10 +11089,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41260</v>
       </c>
       <c r="C15" t="n">
@@ -11109,10 +11121,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11141,10 +11153,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="C17" t="n">
@@ -11173,10 +11185,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41515</v>
       </c>
       <c r="C18" t="n">
@@ -11205,10 +11217,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41624</v>
       </c>
       <c r="C19" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C20" t="n">
@@ -11269,10 +11281,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41788</v>
       </c>
       <c r="C21" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41879</v>
       </c>
       <c r="C22" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41992</v>
       </c>
       <c r="C23" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="C24" t="n">
@@ -11397,10 +11409,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="C25" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42243</v>
       </c>
       <c r="C26" t="n">
@@ -11461,10 +11473,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="C27" t="n">
@@ -11493,10 +11505,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C28" t="n">
@@ -11525,10 +11537,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42516</v>
       </c>
       <c r="C29" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="C30" t="n">
@@ -11589,10 +11601,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42723</v>
       </c>
       <c r="C31" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C32" t="n">
@@ -11653,10 +11665,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="C33" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="C34" t="n">
@@ -11717,10 +11729,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43087</v>
       </c>
       <c r="C35" t="n">
@@ -11749,10 +11761,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C36" t="n">
@@ -11781,10 +11793,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43219</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="C37" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43310</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43342</v>
       </c>
       <c r="C38" t="n">
@@ -11845,10 +11857,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43451</v>
       </c>
       <c r="C39" t="n">
@@ -11877,10 +11889,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43492</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C40" t="n">
@@ -11909,10 +11921,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43583</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="C41" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43674</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43706</v>
       </c>
       <c r="C42" t="n">
@@ -11973,10 +11985,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43818</v>
       </c>
       <c r="C43" t="n">
@@ -12005,10 +12017,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43863</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C44" t="n">
@@ -12037,10 +12049,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43954</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43979</v>
       </c>
       <c r="C45" t="n">
@@ -12069,10 +12081,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44070</v>
       </c>
       <c r="C46" t="n">
@@ -12101,10 +12113,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="C47" t="n">
@@ -12133,10 +12145,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C48" t="n">
@@ -12165,10 +12177,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44343</v>
       </c>
       <c r="C49" t="n">
@@ -12197,10 +12209,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44434</v>
       </c>
       <c r="C50" t="n">
@@ -12229,10 +12241,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="C51" t="n">
@@ -12261,10 +12273,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C52" t="n">
@@ -12293,10 +12305,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44707</v>
       </c>
       <c r="C53" t="n">
@@ -12325,10 +12337,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="C54" t="n">
@@ -12357,10 +12369,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44910</v>
       </c>
       <c r="C55" t="n">
@@ -12389,10 +12401,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C56" t="n">
@@ -12421,10 +12433,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="C57" t="n">
@@ -12453,10 +12465,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="C58" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="C59" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="C60" t="n">
@@ -12549,10 +12561,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45410</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="C61" t="n">
@@ -12581,10 +12593,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45501</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="C62" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45625</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45638</v>
       </c>
       <c r="C63" t="n">
@@ -12645,10 +12657,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45683</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C64" t="n">
@@ -12677,10 +12689,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45774</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="C65" t="n">
@@ -12709,10 +12721,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45865</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="C66" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="C67" t="n">
@@ -12773,10 +12785,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C68" t="n">
@@ -12805,10 +12817,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="C69" t="n">
@@ -12837,10 +12849,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46236</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="C70" t="n">
@@ -12887,12 +12899,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/DE.xlsx
+++ b/salidas/empresas/DE.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.8260440826416</v>
+        <v>25.8260383605957</v>
       </c>
       <c r="C3" t="n">
         <v>38.1349983215332</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>29.1292839050293</v>
+        <v>29.12930107116699</v>
       </c>
       <c r="C6" t="n">
         <v>42.79999923706055</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>24.81640243530273</v>
+        <v>24.8164005279541</v>
       </c>
       <c r="C8" t="n">
         <v>36.28499984741211</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>29.24921798706055</v>
+        <v>29.24921989440918</v>
       </c>
       <c r="C11" t="n">
         <v>42.56499862670898</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>32.8153190612793</v>
+        <v>32.81532287597656</v>
       </c>
       <c r="C13" t="n">
         <v>47.53499984741211</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>34.61363983154297</v>
+        <v>34.61364364624023</v>
       </c>
       <c r="C14" t="n">
         <v>50.13999938964844</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>37.37847137451172</v>
+        <v>37.37845993041992</v>
       </c>
       <c r="C15" t="n">
         <v>54.14500045776367</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>37.65177536010742</v>
+        <v>37.65177154541016</v>
       </c>
       <c r="C16" t="n">
         <v>54.31999969482422</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>37.91517639160156</v>
+        <v>37.91518402099609</v>
       </c>
       <c r="C17" t="n">
         <v>54.70000076293945</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>41.75175094604492</v>
+        <v>41.75174331665039</v>
       </c>
       <c r="C18" t="n">
         <v>60.23500061035156</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>41.99859237670898</v>
+        <v>41.99858093261719</v>
       </c>
       <c r="C19" t="n">
         <v>60.36999893188477</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>41.88727569580078</v>
+        <v>41.88728713989258</v>
       </c>
       <c r="C20" t="n">
         <v>60.20999908447266</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>51.80907821655273</v>
+        <v>51.80908966064453</v>
       </c>
       <c r="C22" t="n">
         <v>74.20999908447266</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>54.07107543945312</v>
+        <v>54.07106399536133</v>
       </c>
       <c r="C23" t="n">
         <v>77.44999694824219</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>59.97037506103516</v>
+        <v>59.97035980224609</v>
       </c>
       <c r="C24" t="n">
         <v>85.90000152587891</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>65.18680572509766</v>
+        <v>65.18682098388672</v>
       </c>
       <c r="C25" t="n">
         <v>93.12000274658203</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>61.29463958740234</v>
+        <v>61.29462051391602</v>
       </c>
       <c r="C26" t="n">
         <v>87.55999755859375</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>59.64957809448242</v>
+        <v>59.64956665039062</v>
       </c>
       <c r="C27" t="n">
         <v>85.20999908447266</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>56.48517990112305</v>
+        <v>56.48514938354492</v>
       </c>
       <c r="C28" t="n">
         <v>80.44000244140625</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>59.03416061401367</v>
+        <v>59.03417587280273</v>
       </c>
       <c r="C29" t="n">
         <v>84.06999969482422</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>57.11713409423828</v>
+        <v>57.11714172363281</v>
       </c>
       <c r="C30" t="n">
         <v>81.33999633789062</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>50.84339141845703</v>
+        <v>50.84338760375977</v>
       </c>
       <c r="C31" t="n">
         <v>72.12999725341797</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>49.45476531982422</v>
+        <v>49.45476150512695</v>
       </c>
       <c r="C32" t="n">
         <v>70.16000366210938</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>49.7437629699707</v>
+        <v>49.74377822875977</v>
       </c>
       <c r="C33" t="n">
         <v>70.56999969482422</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>35.06179046630859</v>
+        <v>35.06179809570312</v>
       </c>
       <c r="C34" t="n">
         <v>49.5</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>27.31278991699219</v>
+        <v>27.31278800964355</v>
       </c>
       <c r="C35" t="n">
         <v>38.56000137329102</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>24.65658950805664</v>
+        <v>24.65658760070801</v>
       </c>
       <c r="C36" t="n">
         <v>34.81000137329102</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>27.34178352355957</v>
+        <v>27.3417911529541</v>
       </c>
       <c r="C37" t="n">
         <v>38.31999969482422</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>24.78741645812988</v>
+        <v>24.78742599487305</v>
       </c>
       <c r="C38" t="n">
         <v>34.7400016784668</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.61445808410645</v>
+        <v>19.61446189880371</v>
       </c>
       <c r="C39" t="n">
         <v>27.48999977111816</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>23.63740158081055</v>
+        <v>23.63740348815918</v>
       </c>
       <c r="C40" t="n">
         <v>32.86999893188477</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>29.67079925537109</v>
+        <v>29.67080116271973</v>
       </c>
       <c r="C41" t="n">
         <v>41.2599983215332</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.26005554199219</v>
+        <v>31.26004791259766</v>
       </c>
       <c r="C42" t="n">
         <v>43.47000122070312</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>28.92105865478516</v>
+        <v>28.92106628417969</v>
       </c>
       <c r="C43" t="n">
         <v>39.95000076293945</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>31.66475868225098</v>
+        <v>31.66476440429688</v>
       </c>
       <c r="C44" t="n">
         <v>43.7400016784668</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>31.56341552734375</v>
+        <v>31.56341361999512</v>
       </c>
       <c r="C45" t="n">
         <v>43.59999847412109</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>31.27040672302246</v>
+        <v>31.2703971862793</v>
       </c>
       <c r="C46" t="n">
         <v>42.91999816894531</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>33.18655395507812</v>
+        <v>33.18655776977539</v>
       </c>
       <c r="C47" t="n">
         <v>45.54999923706055</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>38.98598861694336</v>
+        <v>38.98600387573242</v>
       </c>
       <c r="C48" t="n">
         <v>53.5099983215332</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>39.60685348510742</v>
+        <v>39.60684967041016</v>
       </c>
       <c r="C49" t="n">
         <v>54.09000015258789</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>36.57537078857422</v>
+        <v>36.57539367675781</v>
       </c>
       <c r="C50" t="n">
         <v>49.95000076293945</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>41.95735168457031</v>
+        <v>41.95735931396484</v>
       </c>
       <c r="C51" t="n">
         <v>57.29999923706055</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>43.74123001098633</v>
+        <v>43.74122619628906</v>
       </c>
       <c r="C52" t="n">
         <v>59.45999908447266</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>42.43178939819336</v>
+        <v>42.43180084228516</v>
       </c>
       <c r="C54" t="n">
         <v>57.68000030517578</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>41.16723251342773</v>
+        <v>41.167236328125</v>
       </c>
       <c r="C55" t="n">
         <v>55.68000030517578</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>49.30011749267578</v>
+        <v>49.30014419555664</v>
       </c>
       <c r="C56" t="n">
         <v>66.68000030517578</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>51.80768203735352</v>
+        <v>51.80770111083984</v>
       </c>
       <c r="C58" t="n">
         <v>69.77999877929688</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>57.0196418762207</v>
+        <v>57.0196647644043</v>
       </c>
       <c r="C59" t="n">
         <v>76.80000305175781</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>55.46051788330078</v>
+        <v>55.46054458618164</v>
       </c>
       <c r="C60" t="n">
         <v>74.69999694824219</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>61.91936111450195</v>
+        <v>61.91935729980469</v>
       </c>
       <c r="C61" t="n">
         <v>83.05000305175781</v>
@@ -1744,7 +1744,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>67.77204895019531</v>
+        <v>67.77204132080078</v>
       </c>
       <c r="C62" t="n">
         <v>90.90000152587891</v>
@@ -1773,7 +1773,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>67.21286773681641</v>
+        <v>67.21287536621094</v>
       </c>
       <c r="C63" t="n">
         <v>90.15000152587891</v>
@@ -1802,7 +1802,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>72.51002502441406</v>
+        <v>72.50995635986328</v>
       </c>
       <c r="C64" t="n">
         <v>96.88999938964844</v>
@@ -1831,7 +1831,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>72.96651458740234</v>
+        <v>72.96650695800781</v>
       </c>
       <c r="C65" t="n">
         <v>97.5</v>
@@ -1860,7 +1860,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>64.42006683349609</v>
+        <v>64.42005920410156</v>
       </c>
       <c r="C66" t="n">
         <v>86.08000183105469</v>
@@ -1889,7 +1889,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>62.01858520507812</v>
+        <v>62.01858139038086</v>
       </c>
       <c r="C67" t="n">
         <v>82.44999694824219</v>
@@ -1918,7 +1918,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>59.0549201965332</v>
+        <v>59.0549430847168</v>
       </c>
       <c r="C68" t="n">
         <v>78.51000213623047</v>
@@ -1947,7 +1947,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>60.79250335693359</v>
+        <v>60.79252624511719</v>
       </c>
       <c r="C69" t="n">
         <v>80.81999969482422</v>
@@ -1976,7 +1976,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>48.85762405395508</v>
+        <v>48.85762786865234</v>
       </c>
       <c r="C70" t="n">
         <v>64.56999969482422</v>
@@ -2005,7 +2005,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>57.43059539794922</v>
+        <v>57.43059158325195</v>
       </c>
       <c r="C71" t="n">
         <v>75.90000152587891</v>
@@ -2034,7 +2034,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>59.96543884277344</v>
+        <v>59.96540832519531</v>
       </c>
       <c r="C72" t="n">
         <v>79.25</v>
@@ -2063,7 +2063,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>58.83528900146484</v>
+        <v>58.83526611328125</v>
       </c>
       <c r="C73" t="n">
         <v>77.34999847412109</v>
@@ -2092,7 +2092,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>65.52890014648438</v>
+        <v>65.52891540527344</v>
       </c>
       <c r="C74" t="n">
         <v>86.15000152587891</v>
@@ -2121,7 +2121,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>63.07962417602539</v>
+        <v>63.07967376708984</v>
       </c>
       <c r="C75" t="n">
         <v>82.93000030517578</v>
@@ -2150,7 +2150,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>61.88100051879883</v>
+        <v>61.88101196289062</v>
       </c>
       <c r="C76" t="n">
         <v>80.90000152587891</v>
@@ -2208,7 +2208,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>56.50370025634766</v>
+        <v>56.50373077392578</v>
       </c>
       <c r="C78" t="n">
         <v>73.87000274658203</v>
@@ -2237,7 +2237,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>62.2347412109375</v>
+        <v>62.23472213745117</v>
       </c>
       <c r="C79" t="n">
         <v>80.87000274658203</v>
@@ -2266,7 +2266,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>59.11798095703125</v>
+        <v>59.11800384521484</v>
       </c>
       <c r="C80" t="n">
         <v>76.81999969482422</v>
@@ -2295,7 +2295,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>57.80204010009766</v>
+        <v>57.80203247070312</v>
       </c>
       <c r="C81" t="n">
         <v>75.11000061035156</v>
@@ -2324,7 +2324,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>63.82561492919922</v>
+        <v>63.82563400268555</v>
       </c>
       <c r="C82" t="n">
         <v>82.47000122070312</v>
@@ -2353,7 +2353,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>66.12418365478516</v>
+        <v>66.12419128417969</v>
       </c>
       <c r="C83" t="n">
         <v>85.44000244140625</v>
@@ -2382,7 +2382,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>65.04843902587891</v>
+        <v>65.04842376708984</v>
       </c>
       <c r="C84" t="n">
         <v>84.05000305175781</v>
@@ -2411,7 +2411,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>67.24012756347656</v>
+        <v>67.24015808105469</v>
       </c>
       <c r="C85" t="n">
         <v>86.41999816894531</v>
@@ -2440,7 +2440,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>73.18450927734375</v>
+        <v>73.18453216552734</v>
       </c>
       <c r="C86" t="n">
         <v>94.05999755859375</v>
@@ -2469,7 +2469,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>68.33719635009766</v>
+        <v>68.33718872070312</v>
       </c>
       <c r="C87" t="n">
         <v>87.83000183105469</v>
@@ -2498,7 +2498,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>67.29280090332031</v>
+        <v>67.29278564453125</v>
       </c>
       <c r="C88" t="n">
         <v>85.98000335693359</v>
@@ -2527,7 +2527,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>69.8912353515625</v>
+        <v>69.89124298095703</v>
       </c>
       <c r="C89" t="n">
         <v>89.30000305175781</v>
@@ -2556,7 +2556,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>68.17718505859375</v>
+        <v>68.17722320556641</v>
       </c>
       <c r="C90" t="n">
         <v>87.11000061035156</v>
@@ -2585,7 +2585,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>63.98660278320312</v>
+        <v>63.98663711547852</v>
       </c>
       <c r="C91" t="n">
         <v>81.25</v>
@@ -2643,7 +2643,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>65.86882781982422</v>
+        <v>65.86881256103516</v>
       </c>
       <c r="C93" t="n">
         <v>83.63999938964844</v>
@@ -2672,7 +2672,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>64.48544311523438</v>
+        <v>64.48545074462891</v>
       </c>
       <c r="C94" t="n">
         <v>81.38999938964844</v>
@@ -2701,7 +2701,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>64.84197998046875</v>
+        <v>64.84195709228516</v>
       </c>
       <c r="C95" t="n">
         <v>81.83999633789062</v>
@@ -2730,7 +2730,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>66.74348449707031</v>
+        <v>66.74349212646484</v>
       </c>
       <c r="C96" t="n">
         <v>84.23999786376953</v>
@@ -2759,7 +2759,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>72.76822662353516</v>
+        <v>72.76820373535156</v>
       </c>
       <c r="C97" t="n">
         <v>91.33000183105469</v>
@@ -2817,7 +2817,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>68.46567535400391</v>
+        <v>68.46568298339844</v>
       </c>
       <c r="C99" t="n">
         <v>85.93000030517578</v>
@@ -2846,7 +2846,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>72.76605224609375</v>
+        <v>72.76605987548828</v>
       </c>
       <c r="C100" t="n">
         <v>90.80000305175781</v>
@@ -2904,7 +2904,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>73.06254577636719</v>
+        <v>73.06256866455078</v>
       </c>
       <c r="C102" t="n">
         <v>91.16999816894531</v>
@@ -2933,7 +2933,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>73.04872131347656</v>
+        <v>73.04875183105469</v>
       </c>
       <c r="C103" t="n">
         <v>90.55000305175781</v>
@@ -2962,7 +2962,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>68.66014862060547</v>
+        <v>68.66016387939453</v>
       </c>
       <c r="C104" t="n">
         <v>85.11000061035156</v>
@@ -2991,7 +2991,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>67.83731079101562</v>
+        <v>67.8372802734375</v>
       </c>
       <c r="C105" t="n">
         <v>84.08999633789062</v>
@@ -3049,7 +3049,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>69.50874328613281</v>
+        <v>69.50872039794922</v>
       </c>
       <c r="C107" t="n">
         <v>85.54000091552734</v>
@@ -3078,7 +3078,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>70.38633728027344</v>
+        <v>70.38632202148438</v>
       </c>
       <c r="C108" t="n">
         <v>86.62000274658203</v>
@@ -3107,7 +3107,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>72.37078094482422</v>
+        <v>72.37080383300781</v>
       </c>
       <c r="C109" t="n">
         <v>88.47000122070312</v>
@@ -3136,7 +3136,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>69.68769073486328</v>
+        <v>69.68768310546875</v>
       </c>
       <c r="C110" t="n">
         <v>85.19000244140625</v>
@@ -3165,7 +3165,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>74.11319732666016</v>
+        <v>74.11320495605469</v>
       </c>
       <c r="C111" t="n">
         <v>90.59999847412109</v>
@@ -3223,7 +3223,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>74.55602264404297</v>
+        <v>74.55603790283203</v>
       </c>
       <c r="C113" t="n">
         <v>90.51999664306641</v>
@@ -3281,7 +3281,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>80.44789886474609</v>
+        <v>80.44792175292969</v>
       </c>
       <c r="C115" t="n">
         <v>97.05000305175781</v>
@@ -3310,7 +3310,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>78.39215087890625</v>
+        <v>78.39217376708984</v>
       </c>
       <c r="C116" t="n">
         <v>94.56999969482422</v>
@@ -3339,7 +3339,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>67.79011535644531</v>
+        <v>67.79012298583984</v>
       </c>
       <c r="C117" t="n">
         <v>81.77999877929688</v>
@@ -3368,7 +3368,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>61.83039093017578</v>
+        <v>61.83037185668945</v>
       </c>
       <c r="C118" t="n">
         <v>74</v>
@@ -3397,7 +3397,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>65.17253112792969</v>
+        <v>65.17256927490234</v>
       </c>
       <c r="C119" t="n">
         <v>78</v>
@@ -3426,7 +3426,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>66.48433685302734</v>
+        <v>66.48439025878906</v>
       </c>
       <c r="C120" t="n">
         <v>79.56999969482422</v>
@@ -3513,7 +3513,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>67.51356506347656</v>
+        <v>67.51359558105469</v>
       </c>
       <c r="C123" t="n">
         <v>80.18000030517578</v>
@@ -3542,7 +3542,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>65.31634521484375</v>
+        <v>65.31635284423828</v>
       </c>
       <c r="C124" t="n">
         <v>76.98999786376953</v>
@@ -3571,7 +3571,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>71.35679626464844</v>
+        <v>71.35678100585938</v>
       </c>
       <c r="C125" t="n">
         <v>84.11000061035156</v>
@@ -3600,7 +3600,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>69.81276702880859</v>
+        <v>69.812744140625</v>
       </c>
       <c r="C126" t="n">
         <v>82.29000091552734</v>
@@ -3658,7 +3658,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>66.4217529296875</v>
+        <v>66.42176818847656</v>
       </c>
       <c r="C128" t="n">
         <v>77.70999908447266</v>
@@ -3687,7 +3687,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>72.2681884765625</v>
+        <v>72.26816558837891</v>
       </c>
       <c r="C129" t="n">
         <v>84.55000305175781</v>
@@ -3716,7 +3716,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>73.48284149169922</v>
+        <v>73.48281097412109</v>
       </c>
       <c r="C130" t="n">
         <v>85.34999847412109</v>
@@ -3745,7 +3745,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>76.02268218994141</v>
+        <v>76.02267456054688</v>
       </c>
       <c r="C131" t="n">
         <v>88.30000305175781</v>
@@ -3774,7 +3774,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>86.26808166503906</v>
+        <v>86.26809692382812</v>
       </c>
       <c r="C132" t="n">
         <v>100.1999969482422</v>
@@ -3803,7 +3803,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>89.22848510742188</v>
+        <v>89.22850036621094</v>
       </c>
       <c r="C133" t="n">
         <v>103.0400009155273</v>
@@ -3832,7 +3832,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>92.70098876953125</v>
+        <v>92.70099639892578</v>
       </c>
       <c r="C134" t="n">
         <v>107.0500030517578</v>
@@ -3861,7 +3861,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>94.81393432617188</v>
+        <v>94.81391143798828</v>
       </c>
       <c r="C135" t="n">
         <v>109.4899978637695</v>
@@ -3919,7 +3919,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>97.18804931640625</v>
+        <v>97.18806457519531</v>
       </c>
       <c r="C137" t="n">
         <v>111.6100006103516</v>
@@ -3948,7 +3948,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>106.6360626220703</v>
+        <v>106.6360549926758</v>
       </c>
       <c r="C138" t="n">
         <v>122.4599990844727</v>
@@ -3977,7 +3977,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>108.1519165039062</v>
+        <v>108.1519088745117</v>
       </c>
       <c r="C139" t="n">
         <v>123.5899963378906</v>
@@ -4006,7 +4006,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>112.2560653686523</v>
+        <v>112.2560882568359</v>
       </c>
       <c r="C140" t="n">
         <v>128.2799987792969</v>
@@ -4064,7 +4064,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>110.4394302368164</v>
+        <v>110.4394226074219</v>
       </c>
       <c r="C142" t="n">
         <v>125.5899963378906</v>
@@ -4093,7 +4093,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>116.8500289916992</v>
+        <v>116.8499908447266</v>
       </c>
       <c r="C143" t="n">
         <v>132.8800048828125</v>
@@ -4151,7 +4151,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>138.152099609375</v>
+        <v>138.1520843505859</v>
       </c>
       <c r="C145" t="n">
         <v>156.5099945068359</v>
@@ -4180,7 +4180,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>146.8996734619141</v>
+        <v>146.8997344970703</v>
       </c>
       <c r="C146" t="n">
         <v>166.4199981689453</v>
@@ -4209,7 +4209,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>142.0006866455078</v>
+        <v>142.0006713867188</v>
       </c>
       <c r="C147" t="n">
         <v>160.8699951171875</v>
@@ -4238,7 +4238,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>137.6444854736328</v>
+        <v>137.6444702148438</v>
       </c>
       <c r="C148" t="n">
         <v>155.3200073242188</v>
@@ -4267,7 +4267,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>119.929328918457</v>
+        <v>119.9293060302734</v>
       </c>
       <c r="C149" t="n">
         <v>135.3300018310547</v>
@@ -4296,7 +4296,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>132.4956512451172</v>
+        <v>132.4956665039062</v>
       </c>
       <c r="C150" t="n">
         <v>149.5099945068359</v>
@@ -4325,7 +4325,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>124.5070114135742</v>
+        <v>124.5070266723633</v>
       </c>
       <c r="C151" t="n">
         <v>139.8000030517578</v>
@@ -4354,7 +4354,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>128.9511413574219</v>
+        <v>128.9511566162109</v>
       </c>
       <c r="C152" t="n">
         <v>144.7899932861328</v>
@@ -4383,7 +4383,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>128.0694580078125</v>
+        <v>128.0694732666016</v>
       </c>
       <c r="C153" t="n">
         <v>143.8000030517578</v>
@@ -4412,7 +4412,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>134.4943695068359</v>
+        <v>134.4943542480469</v>
       </c>
       <c r="C154" t="n">
         <v>150.3300018310547</v>
@@ -4441,7 +4441,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>121.1728744506836</v>
+        <v>121.1728439331055</v>
       </c>
       <c r="C155" t="n">
         <v>135.4400024414062</v>
@@ -4499,7 +4499,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>134.1514434814453</v>
+        <v>134.1514587402344</v>
       </c>
       <c r="C157" t="n">
         <v>149.1699981689453</v>
@@ -4528,7 +4528,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>147.4883575439453</v>
+        <v>147.4883728027344</v>
       </c>
       <c r="C158" t="n">
         <v>164</v>
@@ -4586,7 +4586,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>144.4407653808594</v>
+        <v>144.4407806396484</v>
       </c>
       <c r="C160" t="n">
         <v>159.8399963378906</v>
@@ -4615,7 +4615,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>149.6729736328125</v>
+        <v>149.6730041503906</v>
       </c>
       <c r="C161" t="n">
         <v>165.6300048828125</v>
@@ -4644,7 +4644,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>126.6658477783203</v>
+        <v>126.6658096313477</v>
       </c>
       <c r="C162" t="n">
         <v>140.1699981689453</v>
@@ -4673,7 +4673,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>150.4335174560547</v>
+        <v>150.4335021972656</v>
       </c>
       <c r="C163" t="n">
         <v>165.7100067138672</v>
@@ -4702,7 +4702,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>150.3790435791016</v>
+        <v>150.3789825439453</v>
       </c>
       <c r="C164" t="n">
         <v>165.6499938964844</v>
@@ -4731,7 +4731,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>140.6291198730469</v>
+        <v>140.6291656494141</v>
       </c>
       <c r="C165" t="n">
         <v>154.9100036621094</v>
@@ -4760,7 +4760,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>153.8322601318359</v>
+        <v>153.832275390625</v>
       </c>
       <c r="C166" t="n">
         <v>168.6799926757812</v>
@@ -4818,7 +4818,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>153.2577056884766</v>
+        <v>153.2576904296875</v>
       </c>
       <c r="C168" t="n">
         <v>168.0500030517578</v>
@@ -4847,7 +4847,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>158.6950988769531</v>
+        <v>158.6951141357422</v>
       </c>
       <c r="C169" t="n">
         <v>173.2599945068359</v>
@@ -4876,7 +4876,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>145.2491302490234</v>
+        <v>145.2491912841797</v>
       </c>
       <c r="C170" t="n">
         <v>158.5800018310547</v>
@@ -4905,7 +4905,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>143.3257293701172</v>
+        <v>143.3256683349609</v>
       </c>
       <c r="C171" t="n">
         <v>156.4799957275391</v>
@@ -4934,7 +4934,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>127.2616348266602</v>
+        <v>127.2616119384766</v>
       </c>
       <c r="C172" t="n">
         <v>138.1600036621094</v>
@@ -4963,7 +4963,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>133.6173095703125</v>
+        <v>133.6173400878906</v>
       </c>
       <c r="C173" t="n">
         <v>145.0599975585938</v>
@@ -4992,7 +4992,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>140.1204223632812</v>
+        <v>140.1203918457031</v>
       </c>
       <c r="C174" t="n">
         <v>152.1199951171875</v>
@@ -5021,7 +5021,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>145.4955749511719</v>
+        <v>145.4955596923828</v>
       </c>
       <c r="C175" t="n">
         <v>157.1499938964844</v>
@@ -5050,7 +5050,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>163.2346343994141</v>
+        <v>163.2346496582031</v>
       </c>
       <c r="C176" t="n">
         <v>176.3099975585938</v>
@@ -5079,7 +5079,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>194.4816589355469</v>
+        <v>194.4816741943359</v>
       </c>
       <c r="C177" t="n">
         <v>210.0599975585938</v>
@@ -5108,7 +5108,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>205.8988189697266</v>
+        <v>205.8988494873047</v>
       </c>
       <c r="C178" t="n">
         <v>221.6300048828125</v>
@@ -5137,7 +5137,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>209.8750152587891</v>
+        <v>209.8750457763672</v>
       </c>
       <c r="C179" t="n">
         <v>225.9100036621094</v>
@@ -5166,7 +5166,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>243.0503387451172</v>
+        <v>243.0503845214844</v>
       </c>
       <c r="C180" t="n">
         <v>261.6199951171875</v>
@@ -5195,7 +5195,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>250.6710205078125</v>
+        <v>250.6709289550781</v>
       </c>
       <c r="C181" t="n">
         <v>269.0499877929688</v>
@@ -5253,7 +5253,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>325.2712707519531</v>
+        <v>325.2713317871094</v>
       </c>
       <c r="C183" t="n">
         <v>349.1199951171875</v>
@@ -5282,7 +5282,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>349.4368591308594</v>
+        <v>349.4369201660156</v>
       </c>
       <c r="C184" t="n">
         <v>374.1400146484375</v>
@@ -5311,7 +5311,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>346.3640747070312</v>
+        <v>346.3641052246094</v>
       </c>
       <c r="C185" t="n">
         <v>370.8500061035156</v>
@@ -5340,7 +5340,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>337.2578735351562</v>
+        <v>337.2578430175781</v>
       </c>
       <c r="C186" t="n">
         <v>361.1000061035156</v>
@@ -5369,7 +5369,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>330.2712707519531</v>
+        <v>330.2712097167969</v>
       </c>
       <c r="C187" t="n">
         <v>352.7099914550781</v>
@@ -5398,7 +5398,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>338.58642578125</v>
+        <v>338.5864562988281</v>
       </c>
       <c r="C188" t="n">
         <v>361.5899963378906</v>
@@ -5427,7 +5427,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>353.9804992675781</v>
+        <v>353.9805908203125</v>
       </c>
       <c r="C189" t="n">
         <v>378.0299987792969</v>
@@ -5456,7 +5456,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>314.6871032714844</v>
+        <v>314.6871337890625</v>
       </c>
       <c r="C190" t="n">
         <v>335.0700073242188</v>
@@ -5485,7 +5485,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>321.4866638183594</v>
+        <v>321.4866943359375</v>
       </c>
       <c r="C191" t="n">
         <v>342.3099975585938</v>
@@ -5514,7 +5514,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>324.5202026367188</v>
+        <v>324.5201721191406</v>
       </c>
       <c r="C192" t="n">
         <v>345.5400085449219</v>
@@ -5572,7 +5572,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>354.579833984375</v>
+        <v>354.5798645019531</v>
       </c>
       <c r="C194" t="n">
         <v>376.3999938964844</v>
@@ -5601,7 +5601,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>339.1494750976562</v>
+        <v>339.1493835449219</v>
       </c>
       <c r="C195" t="n">
         <v>360.0199890136719</v>
@@ -5659,7 +5659,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>356.5699157714844</v>
+        <v>356.5698852539062</v>
       </c>
       <c r="C197" t="n">
         <v>377.5499877929688</v>
@@ -5688,7 +5688,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>337.8984985351562</v>
+        <v>337.8985290527344</v>
       </c>
       <c r="C198" t="n">
         <v>357.7799987792969</v>
@@ -5746,7 +5746,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>325.298828125</v>
+        <v>325.2988586425781</v>
       </c>
       <c r="C200" t="n">
         <v>343.1799926757812</v>
@@ -5775,7 +5775,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>346.2188720703125</v>
+        <v>346.2188110351562</v>
       </c>
       <c r="C201" t="n">
         <v>365.25</v>
@@ -5833,7 +5833,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>376.4257507324219</v>
+        <v>376.42578125</v>
       </c>
       <c r="C203" t="n">
         <v>395.8200073242188</v>
@@ -5862,7 +5862,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>419.3920593261719</v>
+        <v>419.3920288085938</v>
       </c>
       <c r="C204" t="n">
         <v>441</v>
@@ -5891,7 +5891,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>408.8923950195312</v>
+        <v>408.8923645019531</v>
       </c>
       <c r="C205" t="n">
         <v>428.760009765625</v>
@@ -5920,7 +5920,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>403.2467346191406</v>
+        <v>403.2466430664062</v>
       </c>
       <c r="C206" t="n">
         <v>422.8399963378906</v>
@@ -5978,7 +5978,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>394.9801330566406</v>
+        <v>394.9800415039062</v>
       </c>
       <c r="C208" t="n">
         <v>412.8800048828125</v>
@@ -6007,7 +6007,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>361.6314392089844</v>
+        <v>361.6314086914062</v>
       </c>
       <c r="C209" t="n">
         <v>378.0199890136719</v>
@@ -6036,7 +6036,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>330.9804382324219</v>
+        <v>330.98046875</v>
       </c>
       <c r="C210" t="n">
         <v>345.9800109863281</v>
@@ -6123,7 +6123,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>394.3407287597656</v>
+        <v>394.3406677246094</v>
       </c>
       <c r="C213" t="n">
         <v>410.9400024414062</v>
@@ -6181,7 +6181,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>351.8375549316406</v>
+        <v>351.8376159667969</v>
       </c>
       <c r="C215" t="n">
         <v>365.3599853515625</v>
@@ -6210,7 +6210,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>350.9228210449219</v>
+        <v>350.9227600097656</v>
       </c>
       <c r="C216" t="n">
         <v>364.4100036621094</v>
@@ -6239,7 +6239,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>386.48486328125</v>
+        <v>386.4848937988281</v>
       </c>
       <c r="C217" t="n">
         <v>399.8699951171875</v>
@@ -6268,7 +6268,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>380.4054565429688</v>
+        <v>380.4054870605469</v>
       </c>
       <c r="C218" t="n">
         <v>393.5799865722656</v>
@@ -6297,7 +6297,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>352.8304748535156</v>
+        <v>352.8304443359375</v>
       </c>
       <c r="C219" t="n">
         <v>365.0499877929688</v>
@@ -6326,7 +6326,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>398.4608154296875</v>
+        <v>398.4608459472656</v>
       </c>
       <c r="C220" t="n">
         <v>410.739990234375</v>
@@ -6355,7 +6355,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>379.7086486816406</v>
+        <v>379.7087097167969</v>
       </c>
       <c r="C221" t="n">
         <v>391.4100036621094</v>
@@ -6384,7 +6384,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>363.5564575195312</v>
+        <v>363.5564880371094</v>
       </c>
       <c r="C222" t="n">
         <v>374.760009765625</v>
@@ -6413,7 +6413,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>363.8798217773438</v>
+        <v>363.8798828125</v>
       </c>
       <c r="C223" t="n">
         <v>373.6300048828125</v>
@@ -6442,7 +6442,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>362.2729187011719</v>
+        <v>362.27294921875</v>
       </c>
       <c r="C224" t="n">
         <v>371.9800109863281</v>
@@ -6500,7 +6500,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>407.8738708496094</v>
+        <v>407.8738403320312</v>
       </c>
       <c r="C226" t="n">
         <v>417.3299865722656</v>
@@ -6529,7 +6529,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>395.520263671875</v>
+        <v>395.5202941894531</v>
       </c>
       <c r="C227" t="n">
         <v>404.6900024414062</v>
@@ -6587,7 +6587,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>415.6853637695312</v>
+        <v>415.6853942871094</v>
       </c>
       <c r="C229" t="n">
         <v>423.7000122070312</v>
@@ -6616,7 +6616,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>467.5454711914062</v>
+        <v>467.5455017089844</v>
       </c>
       <c r="C230" t="n">
         <v>476.5599975585938</v>
@@ -6645,7 +6645,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>471.6954345703125</v>
+        <v>471.6954650878906</v>
       </c>
       <c r="C231" t="n">
         <v>480.7900085449219</v>
@@ -6674,7 +6674,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>462.0805969238281</v>
+        <v>462.0806274414062</v>
       </c>
       <c r="C232" t="n">
         <v>469.3500061035156</v>
@@ -6703,7 +6703,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>456.3802795410156</v>
+        <v>456.3803100585938</v>
       </c>
       <c r="C233" t="n">
         <v>463.5599975585938</v>
@@ -6732,7 +6732,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>498.4189758300781</v>
+        <v>498.4189453125</v>
       </c>
       <c r="C234" t="n">
         <v>506.260009765625</v>
@@ -6761,7 +6761,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>502.19921875</v>
+        <v>502.1992492675781</v>
       </c>
       <c r="C235" t="n">
         <v>508.489990234375</v>
@@ -6819,7 +6819,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>472.7185668945312</v>
+        <v>472.7185363769531</v>
       </c>
       <c r="C237" t="n">
         <v>478.6400146484375</v>
